--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2024_valparaiso.xlsx
@@ -158,7 +158,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:33</t>
+    <t xml:space="preserve">2026-09-10 01:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2024_valparaiso.xlsx
@@ -158,7 +158,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:50</t>
+    <t xml:space="preserve">2026-09-12 23:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2024_valparaiso.xlsx
@@ -158,7 +158,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 23:01</t>
+    <t xml:space="preserve">2026-09-23 15:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2024_valparaiso.xlsx
@@ -41,7 +41,7 @@
     <t xml:space="preserve">Llaillay</t>
   </si>
   <si>
-    <t xml:space="preserve">Juan Fernandez</t>
+    <t xml:space="preserve">Juan Fernández</t>
   </si>
   <si>
     <t xml:space="preserve">Calle Larga</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:53</t>
+    <t xml:space="preserve">2026-10-04 10:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2024_valparaiso.xlsx
@@ -158,7 +158,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:52</t>
+    <t xml:space="preserve">2026-10-05 17:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
